--- a/dados/brutos/comercial_espelho.xlsx
+++ b/dados/brutos/comercial_espelho.xlsx
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,9 +52,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,8 +618,8 @@
           <t>Pré-lançamento</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr"/>
+      <c r="G6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -643,8 +645,8 @@
           <t>Pré-lançamento</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -662,8 +664,8 @@
           <t>Pré-lançamento</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr"/>
+      <c r="G8" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14139,7 +14141,7 @@
       <c r="K2" t="n">
         <v>396404.5</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="M2" t="inlineStr">
@@ -14147,7 +14149,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -14195,7 +14197,7 @@
       <c r="K3" t="n">
         <v>257909.47</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>2.27</v>
       </c>
       <c r="M3" t="inlineStr">
@@ -14253,7 +14255,7 @@
       <c r="K4" t="n">
         <v>313782.26</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="2" t="n">
         <v>0.89</v>
       </c>
       <c r="M4" t="inlineStr">
@@ -14261,7 +14263,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -14309,7 +14311,7 @@
       <c r="K5" t="n">
         <v>548026.96</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="2" t="n">
         <v>5.48</v>
       </c>
       <c r="M5" t="inlineStr">
@@ -14317,7 +14319,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -14365,7 +14367,7 @@
       <c r="K6" t="n">
         <v>370698.75</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="2" t="n">
         <v>0.75</v>
       </c>
       <c r="M6" t="inlineStr">
@@ -14373,7 +14375,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -14421,7 +14423,7 @@
       <c r="K7" t="n">
         <v>368983.72</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="2" t="n">
         <v>4.68</v>
       </c>
       <c r="M7" t="inlineStr">
@@ -14479,7 +14481,7 @@
       <c r="K8" t="n">
         <v>285494.46</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="2" t="n">
         <v>2.86</v>
       </c>
       <c r="M8" t="inlineStr">
@@ -14487,7 +14489,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14535,7 +14537,7 @@
       <c r="K9" t="n">
         <v>504236.61</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="2" t="n">
         <v>3.79</v>
       </c>
       <c r="M9" t="inlineStr">
@@ -14593,7 +14595,7 @@
       <c r="K10" t="n">
         <v>353829.63</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="2" t="n">
         <v>2.23</v>
       </c>
       <c r="M10" t="inlineStr">
@@ -14601,7 +14603,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14649,7 +14651,7 @@
       <c r="K11" t="n">
         <v>350019.76</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="M11" t="inlineStr">
@@ -14707,7 +14709,7 @@
       <c r="K12" t="n">
         <v>277878.12</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="2" t="n">
         <v>0.64</v>
       </c>
       <c r="M12" t="inlineStr">
@@ -14715,7 +14717,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14763,7 +14765,7 @@
       <c r="K13" t="n">
         <v>587609.55</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="2" t="n">
         <v>1.93</v>
       </c>
       <c r="M13" t="inlineStr">
@@ -14771,7 +14773,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14819,7 +14821,7 @@
       <c r="K14" t="n">
         <v>277345.67</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="2" t="n">
         <v>2.72</v>
       </c>
       <c r="M14" t="inlineStr">
@@ -14827,7 +14829,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14875,7 +14877,7 @@
       <c r="K15" t="n">
         <v>479791.62</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="2" t="n">
         <v>1.42</v>
       </c>
       <c r="M15" t="inlineStr">
@@ -14883,7 +14885,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14931,7 +14933,7 @@
       <c r="K16" t="n">
         <v>482341.29</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="2" t="n">
         <v>1.95</v>
       </c>
       <c r="M16" t="inlineStr">
@@ -14939,7 +14941,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14987,7 +14989,7 @@
       <c r="K17" t="n">
         <v>319425.12</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="2" t="n">
         <v>5.92</v>
       </c>
       <c r="M17" t="inlineStr">
@@ -14995,7 +14997,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15043,7 +15045,7 @@
       <c r="K18" t="n">
         <v>308415.86</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="M18" t="inlineStr">
@@ -15051,7 +15053,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,7 +15101,7 @@
       <c r="K19" t="n">
         <v>288279.36</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="2" t="n">
         <v>4.48</v>
       </c>
       <c r="M19" t="inlineStr">
@@ -15107,7 +15109,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15155,7 +15157,7 @@
       <c r="K20" t="n">
         <v>296011.96</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="2" t="n">
         <v>0.12</v>
       </c>
       <c r="M20" t="inlineStr">
@@ -15163,7 +15165,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15211,7 +15213,7 @@
       <c r="K21" t="n">
         <v>649136.87</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="2" t="n">
         <v>2.88</v>
       </c>
       <c r="M21" t="inlineStr">
@@ -15219,7 +15221,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15267,7 +15269,7 @@
       <c r="K22" t="n">
         <v>321798.22</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="M22" t="inlineStr">
@@ -15325,7 +15327,7 @@
       <c r="K23" t="n">
         <v>265319.65</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="2" t="n">
         <v>1.59</v>
       </c>
       <c r="M23" t="inlineStr">
@@ -15333,7 +15335,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15381,7 +15383,7 @@
       <c r="K24" t="n">
         <v>333207.18</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="2" t="n">
         <v>1.63</v>
       </c>
       <c r="M24" t="inlineStr">
@@ -15389,7 +15391,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -15437,7 +15439,7 @@
       <c r="K25" t="n">
         <v>350220.16</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="2" t="n">
         <v>1.24</v>
       </c>
       <c r="M25" t="inlineStr">
@@ -15445,7 +15447,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -15493,7 +15495,7 @@
       <c r="K26" t="n">
         <v>589714.92</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="2" t="n">
         <v>3.27</v>
       </c>
       <c r="M26" t="inlineStr">
@@ -15501,7 +15503,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" s="1" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -15549,7 +15551,7 @@
       <c r="K27" t="n">
         <v>386940.19</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="2" t="n">
         <v>2.39</v>
       </c>
       <c r="M27" t="inlineStr">
@@ -15557,7 +15559,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15605,7 +15607,7 @@
       <c r="K28" t="n">
         <v>352282.85</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="2" t="n">
         <v>5.1</v>
       </c>
       <c r="M28" t="inlineStr">
@@ -15613,7 +15615,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15661,7 +15663,7 @@
       <c r="K29" t="n">
         <v>331828.49</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="2" t="n">
         <v>4.1</v>
       </c>
       <c r="M29" t="inlineStr">
@@ -15719,7 +15721,7 @@
       <c r="K30" t="n">
         <v>311948.8</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="2" t="n">
         <v>5.91</v>
       </c>
       <c r="M30" t="inlineStr">
@@ -15727,7 +15729,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -15775,7 +15777,7 @@
       <c r="K31" t="n">
         <v>239347.3</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="2" t="n">
         <v>10.68</v>
       </c>
       <c r="M31" t="inlineStr">
@@ -15783,7 +15785,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -15831,7 +15833,7 @@
       <c r="K32" t="n">
         <v>306391.27</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="2" t="n">
         <v>2.45</v>
       </c>
       <c r="M32" t="inlineStr">
@@ -15839,7 +15841,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -15887,7 +15889,7 @@
       <c r="K33" t="n">
         <v>272736.24</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="2" t="n">
         <v>1.63</v>
       </c>
       <c r="M33" t="inlineStr">
@@ -15895,7 +15897,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" s="1" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -15943,7 +15945,7 @@
       <c r="K34" t="n">
         <v>497223.23</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="2" t="n">
         <v>6.19</v>
       </c>
       <c r="M34" t="inlineStr">
@@ -15951,7 +15953,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -15999,7 +16001,7 @@
       <c r="K35" t="n">
         <v>302439.95</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="2" t="n">
         <v>2.19</v>
       </c>
       <c r="M35" t="inlineStr">
@@ -16007,7 +16009,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" s="1" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -16055,7 +16057,7 @@
       <c r="K36" t="n">
         <v>267357.46</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" s="2" t="n">
         <v>1.44</v>
       </c>
       <c r="M36" t="inlineStr">
@@ -16063,7 +16065,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -16111,7 +16113,7 @@
       <c r="K37" t="n">
         <v>380879.92</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="2" t="n">
         <v>3.48</v>
       </c>
       <c r="M37" t="inlineStr">
@@ -16119,7 +16121,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -16167,7 +16169,7 @@
       <c r="K38" t="n">
         <v>332101.61</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="2" t="n">
         <v>2.97</v>
       </c>
       <c r="M38" t="inlineStr">
@@ -16175,7 +16177,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" s="1" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -16223,7 +16225,7 @@
       <c r="K39" t="n">
         <v>339329.21</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="2" t="n">
         <v>1.36</v>
       </c>
       <c r="M39" t="inlineStr">
@@ -16231,7 +16233,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" s="1" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -16275,7 +16277,7 @@
       <c r="K40" t="n">
         <v>331787.4</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="2" t="n">
         <v>4.82</v>
       </c>
       <c r="M40" t="inlineStr">
@@ -16283,7 +16285,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" s="1" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -16331,7 +16333,7 @@
       <c r="K41" t="n">
         <v>571187.24</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="M41" t="inlineStr">
@@ -16339,7 +16341,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" s="1" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -16387,7 +16389,7 @@
       <c r="K42" t="n">
         <v>359019.92</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" s="2" t="n">
         <v>2.3</v>
       </c>
       <c r="M42" t="inlineStr">
@@ -16395,7 +16397,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" s="1" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -16443,7 +16445,7 @@
       <c r="K43" t="n">
         <v>357889.39</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43" s="2" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="M43" t="inlineStr">
@@ -16451,7 +16453,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -16495,7 +16497,7 @@
       <c r="K44" t="n">
         <v>519351.73</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44" s="2" t="n">
         <v>6.1</v>
       </c>
       <c r="M44" t="inlineStr">
@@ -16503,7 +16505,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" s="1" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -16551,7 +16553,7 @@
       <c r="K45" t="n">
         <v>356105.22</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45" s="2" t="n">
         <v>5.3</v>
       </c>
       <c r="M45" t="inlineStr">
@@ -16559,7 +16561,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" s="1" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -16607,7 +16609,7 @@
       <c r="K46" t="n">
         <v>362131.67</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46" s="2" t="n">
         <v>6.47</v>
       </c>
       <c r="M46" t="inlineStr">
@@ -16615,7 +16617,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" s="1" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -16659,7 +16661,7 @@
       <c r="K47" t="n">
         <v>284085.93</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47" s="2" t="n">
         <v>6.93</v>
       </c>
       <c r="M47" t="inlineStr">
@@ -16667,7 +16669,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" s="1" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -16711,7 +16713,7 @@
       <c r="K48" t="n">
         <v>557200.71</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48" s="2" t="n">
         <v>1.97</v>
       </c>
       <c r="M48" t="inlineStr">
@@ -16719,7 +16721,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" s="1" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -16767,7 +16769,7 @@
       <c r="K49" t="n">
         <v>278276.46</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="M49" t="inlineStr">
@@ -16775,7 +16777,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -16823,7 +16825,7 @@
       <c r="K50" t="n">
         <v>284514.36</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50" s="2" t="n">
         <v>4.01</v>
       </c>
       <c r="M50" t="inlineStr">
@@ -16831,7 +16833,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -16879,7 +16881,7 @@
       <c r="K51" t="n">
         <v>278838.11</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51" s="2" t="n">
         <v>2.81</v>
       </c>
       <c r="M51" t="inlineStr">
@@ -16887,7 +16889,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -16935,7 +16937,7 @@
       <c r="K52" t="n">
         <v>266102.06</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52" s="2" t="n">
         <v>6.71</v>
       </c>
       <c r="M52" t="inlineStr">
@@ -16993,7 +16995,7 @@
       <c r="K53" t="n">
         <v>273674.52</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53" s="2" t="n">
         <v>6.34</v>
       </c>
       <c r="M53" t="inlineStr">
@@ -17001,7 +17003,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -17045,7 +17047,7 @@
       <c r="K54" t="n">
         <v>303413.58</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54" s="2" t="n">
         <v>0.91</v>
       </c>
       <c r="M54" t="inlineStr">
@@ -17053,7 +17055,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -17101,7 +17103,7 @@
       <c r="K55" t="n">
         <v>313245.05</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L55" s="2" t="n">
         <v>3.17</v>
       </c>
       <c r="M55" t="inlineStr">
@@ -17109,7 +17111,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" s="1" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -17157,7 +17159,7 @@
       <c r="K56" t="n">
         <v>296921.92</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L56" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="M56" t="inlineStr">
@@ -17165,7 +17167,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" s="1" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -17213,7 +17215,7 @@
       <c r="K57" t="n">
         <v>282385.88</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57" s="2" t="n">
         <v>1.16</v>
       </c>
       <c r="M57" t="inlineStr">
@@ -17221,7 +17223,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" s="1" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -17269,7 +17271,7 @@
       <c r="K58" t="n">
         <v>282504.8</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58" s="2" t="n">
         <v>2.45</v>
       </c>
       <c r="M58" t="inlineStr">
@@ -17277,7 +17279,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" s="1" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -17325,7 +17327,7 @@
       <c r="K59" t="n">
         <v>308795.6</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="M59" t="inlineStr">
@@ -17333,7 +17335,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" s="1" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -17381,7 +17383,7 @@
       <c r="K60" t="n">
         <v>266063.8</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60" s="2" t="n">
         <v>1.64</v>
       </c>
       <c r="M60" t="inlineStr">
@@ -17389,7 +17391,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" s="1" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -17437,7 +17439,7 @@
       <c r="K61" t="n">
         <v>261125.37</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61" s="2" t="n">
         <v>2.31</v>
       </c>
       <c r="M61" t="inlineStr">
@@ -17445,7 +17447,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" s="1" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -17493,7 +17495,7 @@
       <c r="K62" t="n">
         <v>263505.6</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62" s="2" t="n">
         <v>5.35</v>
       </c>
       <c r="M62" t="inlineStr">
@@ -17501,7 +17503,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" s="1" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -17549,7 +17551,7 @@
       <c r="K63" t="n">
         <v>310501.6</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63" s="2" t="n">
         <v>1.74</v>
       </c>
       <c r="M63" t="inlineStr">
@@ -17607,7 +17609,7 @@
       <c r="K64" t="n">
         <v>302926.91</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64" s="2" t="n">
         <v>4.71</v>
       </c>
       <c r="M64" t="inlineStr">
@@ -17615,7 +17617,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" s="1" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -17663,7 +17665,7 @@
       <c r="K65" t="n">
         <v>338684.15</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L65" s="2" t="n">
         <v>0.65</v>
       </c>
       <c r="M65" t="inlineStr">
@@ -17671,7 +17673,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" s="1" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -17719,7 +17721,7 @@
       <c r="K66" t="n">
         <v>618623.1800000001</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66" s="2" t="n">
         <v>1.27</v>
       </c>
       <c r="M66" t="inlineStr">
@@ -17727,7 +17729,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" s="1" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -17775,7 +17777,7 @@
       <c r="K67" t="n">
         <v>307810.49</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67" s="2" t="n">
         <v>0.93</v>
       </c>
       <c r="M67" t="inlineStr">
@@ -17783,7 +17785,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" s="1" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -17831,7 +17833,7 @@
       <c r="K68" t="n">
         <v>311544.6</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68" s="2" t="n">
         <v>2.03</v>
       </c>
       <c r="M68" t="inlineStr">
@@ -17839,7 +17841,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" s="1" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -17887,7 +17889,7 @@
       <c r="K69" t="n">
         <v>295536.84</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69" s="2" t="n">
         <v>11.09</v>
       </c>
       <c r="M69" t="inlineStr">
@@ -17895,7 +17897,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" s="1" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -17943,7 +17945,7 @@
       <c r="K70" t="n">
         <v>321414.66</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L70" s="2" t="n">
         <v>3.13</v>
       </c>
       <c r="M70" t="inlineStr">
@@ -17951,7 +17953,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" s="1" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -17999,7 +18001,7 @@
       <c r="K71" t="n">
         <v>347323.47</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71" s="2" t="n">
         <v>3.99</v>
       </c>
       <c r="M71" t="inlineStr">
@@ -18007,7 +18009,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" s="1" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -18055,7 +18057,7 @@
       <c r="K72" t="n">
         <v>341699.41</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L72" s="2" t="n">
         <v>2.62</v>
       </c>
       <c r="M72" t="inlineStr">
@@ -18063,7 +18065,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" s="1" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -18111,7 +18113,7 @@
       <c r="K73" t="n">
         <v>296899.31</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73" s="2" t="n">
         <v>1.03</v>
       </c>
       <c r="M73" t="inlineStr">
@@ -18119,7 +18121,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" s="1" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -18167,7 +18169,7 @@
       <c r="K74" t="n">
         <v>316906.9</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="M74" t="inlineStr">
@@ -18175,7 +18177,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" s="1" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -18223,7 +18225,7 @@
       <c r="K75" t="n">
         <v>296958.38</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75" s="2" t="n">
         <v>6.26</v>
       </c>
       <c r="M75" t="inlineStr">
@@ -18231,7 +18233,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" s="1" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -18279,7 +18281,7 @@
       <c r="K76" t="n">
         <v>336176.31</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76" s="2" t="n">
         <v>2.06</v>
       </c>
       <c r="M76" t="inlineStr">
@@ -18287,7 +18289,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" s="1" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -18335,7 +18337,7 @@
       <c r="K77" t="n">
         <v>350882.86</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77" s="2" t="n">
         <v>3.06</v>
       </c>
       <c r="M77" t="inlineStr">
@@ -18343,7 +18345,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" s="1" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -18391,7 +18393,7 @@
       <c r="K78" t="n">
         <v>266012.78</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78" s="2" t="n">
         <v>3.74</v>
       </c>
       <c r="M78" t="inlineStr">
@@ -18399,7 +18401,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" s="1" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -18447,7 +18449,7 @@
       <c r="K79" t="n">
         <v>294811.32</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79" s="2" t="n">
         <v>0.66</v>
       </c>
       <c r="M79" t="inlineStr">
@@ -18455,7 +18457,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" s="1" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -18503,7 +18505,7 @@
       <c r="K80" t="n">
         <v>299133.7</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="M80" t="inlineStr">
@@ -18511,7 +18513,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" s="1" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -18559,7 +18561,7 @@
       <c r="K81" t="n">
         <v>277913.09</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81" s="2" t="n">
         <v>10.19</v>
       </c>
       <c r="M81" t="inlineStr">
@@ -18567,7 +18569,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" s="1" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -18615,7 +18617,7 @@
       <c r="K82" t="n">
         <v>531019.63</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L82" s="2" t="n">
         <v>6.57</v>
       </c>
       <c r="M82" t="inlineStr">
@@ -18623,7 +18625,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" s="1" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -18671,7 +18673,7 @@
       <c r="K83" t="n">
         <v>296810.4</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="M83" t="inlineStr">
@@ -18679,7 +18681,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" s="1" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -18727,7 +18729,7 @@
       <c r="K84" t="n">
         <v>302442.26</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84" s="2" t="n">
         <v>3.97</v>
       </c>
       <c r="M84" t="inlineStr">
@@ -18735,7 +18737,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" s="1" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -18783,7 +18785,7 @@
       <c r="K85" t="n">
         <v>314287.89</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85" s="2" t="n">
         <v>4.71</v>
       </c>
       <c r="M85" t="inlineStr">
@@ -18791,7 +18793,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" s="1" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -18839,7 +18841,7 @@
       <c r="K86" t="n">
         <v>353641.41</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86" s="2" t="n">
         <v>2.27</v>
       </c>
       <c r="M86" t="inlineStr">
@@ -18847,7 +18849,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" s="1" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -18895,7 +18897,7 @@
       <c r="K87" t="n">
         <v>258236.47</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87" s="2" t="n">
         <v>11.86</v>
       </c>
       <c r="M87" t="inlineStr">
@@ -18903,7 +18905,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" s="1" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -18947,7 +18949,7 @@
       <c r="K88" t="n">
         <v>355030.66</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L88" s="2" t="n">
         <v>5.11</v>
       </c>
       <c r="M88" t="inlineStr">
@@ -18955,7 +18957,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" s="1" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -19003,7 +19005,7 @@
       <c r="K89" t="n">
         <v>399303.75</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89" s="2" t="n">
         <v>6.57</v>
       </c>
       <c r="M89" t="inlineStr">
@@ -19061,7 +19063,7 @@
       <c r="K90" t="n">
         <v>300713.56</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90" s="2" t="n">
         <v>5.31</v>
       </c>
       <c r="M90" t="inlineStr">
@@ -19069,7 +19071,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" s="1" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -19117,7 +19119,7 @@
       <c r="K91" t="n">
         <v>313446.68</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91" s="2" t="n">
         <v>4.26</v>
       </c>
       <c r="M91" t="inlineStr">
@@ -19125,7 +19127,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
+      <c r="N91" s="1" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -19173,7 +19175,7 @@
       <c r="K92" t="n">
         <v>360384.08</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92" s="2" t="n">
         <v>3.64</v>
       </c>
       <c r="M92" t="inlineStr">
@@ -19181,7 +19183,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" s="1" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -19225,7 +19227,7 @@
       <c r="K93" t="n">
         <v>320104.17</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93" s="2" t="n">
         <v>1.71</v>
       </c>
       <c r="M93" t="inlineStr">
@@ -19233,7 +19235,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" s="1" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -19281,7 +19283,7 @@
       <c r="K94" t="n">
         <v>278614.92</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94" s="2" t="n">
         <v>2.41</v>
       </c>
       <c r="M94" t="inlineStr">
@@ -19289,7 +19291,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" s="1" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -19337,7 +19339,7 @@
       <c r="K95" t="n">
         <v>352856.31</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95" s="2" t="n">
         <v>1.68</v>
       </c>
       <c r="M95" t="inlineStr">
@@ -19345,7 +19347,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" s="1" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -19393,7 +19395,7 @@
       <c r="K96" t="n">
         <v>293325.36</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96" s="2" t="n">
         <v>1.8</v>
       </c>
       <c r="M96" t="inlineStr">
@@ -19451,7 +19453,7 @@
       <c r="K97" t="n">
         <v>284551.53</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97" s="2" t="n">
         <v>1.58</v>
       </c>
       <c r="M97" t="inlineStr">
@@ -19459,7 +19461,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" s="1" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -19507,7 +19509,7 @@
       <c r="K98" t="n">
         <v>328436.93</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98" s="2" t="n">
         <v>1.86</v>
       </c>
       <c r="M98" t="inlineStr">
@@ -19515,7 +19517,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" s="1" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -19563,7 +19565,7 @@
       <c r="K99" t="n">
         <v>325988.27</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99" s="2" t="n">
         <v>2.98</v>
       </c>
       <c r="M99" t="inlineStr">
@@ -19571,7 +19573,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" s="1" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -19615,7 +19617,7 @@
       <c r="K100" t="n">
         <v>312579.41</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100" s="2" t="n">
         <v>0.23</v>
       </c>
       <c r="M100" t="inlineStr">
@@ -19623,7 +19625,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" s="1" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -19671,7 +19673,7 @@
       <c r="K101" t="n">
         <v>324457.05</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101" s="2" t="n">
         <v>1.05</v>
       </c>
       <c r="M101" t="inlineStr">
@@ -19679,7 +19681,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" s="1" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -19727,7 +19729,7 @@
       <c r="K102" t="n">
         <v>309822.24</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102" s="2" t="n">
         <v>3.12</v>
       </c>
       <c r="M102" t="inlineStr">
@@ -19735,7 +19737,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" s="1" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -19783,7 +19785,7 @@
       <c r="K103" t="n">
         <v>372284.75</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103" s="2" t="n">
         <v>2.84</v>
       </c>
       <c r="M103" t="inlineStr">
@@ -19791,7 +19793,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
+      <c r="N103" s="1" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -19839,7 +19841,7 @@
       <c r="K104" t="n">
         <v>369967.92</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104" s="2" t="n">
         <v>2.28</v>
       </c>
       <c r="M104" t="inlineStr">
@@ -19847,7 +19849,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
+      <c r="N104" s="1" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -19895,7 +19897,7 @@
       <c r="K105" t="n">
         <v>294959.25</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105" s="2" t="n">
         <v>2.75</v>
       </c>
       <c r="M105" t="inlineStr">
@@ -19903,7 +19905,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" s="1" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -19951,7 +19953,7 @@
       <c r="K106" t="n">
         <v>287512.82</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L106" s="2" t="n">
         <v>2.67</v>
       </c>
       <c r="M106" t="inlineStr">
@@ -19959,7 +19961,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" s="1" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -20003,7 +20005,7 @@
       <c r="K107" t="n">
         <v>360412.32</v>
       </c>
-      <c r="L107" t="n">
+      <c r="L107" s="2" t="n">
         <v>2.88</v>
       </c>
       <c r="M107" t="inlineStr">
@@ -20011,7 +20013,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" s="1" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -20059,7 +20061,7 @@
       <c r="K108" t="n">
         <v>354972.38</v>
       </c>
-      <c r="L108" t="n">
+      <c r="L108" s="2" t="n">
         <v>3.75</v>
       </c>
       <c r="M108" t="inlineStr">
@@ -20067,7 +20069,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
+      <c r="N108" s="1" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -20115,7 +20117,7 @@
       <c r="K109" t="n">
         <v>317261.76</v>
       </c>
-      <c r="L109" t="n">
+      <c r="L109" s="2" t="n">
         <v>9.92</v>
       </c>
       <c r="M109" t="inlineStr">
@@ -20123,7 +20125,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
+      <c r="N109" s="1" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -20171,7 +20173,7 @@
       <c r="K110" t="n">
         <v>277401.24</v>
       </c>
-      <c r="L110" t="n">
+      <c r="L110" s="2" t="n">
         <v>6.22</v>
       </c>
       <c r="M110" t="inlineStr">
@@ -20179,7 +20181,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" s="1" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -20227,7 +20229,7 @@
       <c r="K111" t="n">
         <v>321780.36</v>
       </c>
-      <c r="L111" t="n">
+      <c r="L111" s="2" t="n">
         <v>4.74</v>
       </c>
       <c r="M111" t="inlineStr">
@@ -20235,7 +20237,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
+      <c r="N111" s="1" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -20283,7 +20285,7 @@
       <c r="K112" t="n">
         <v>304588.36</v>
       </c>
-      <c r="L112" t="n">
+      <c r="L112" s="2" t="n">
         <v>0.27</v>
       </c>
       <c r="M112" t="inlineStr">
@@ -20291,7 +20293,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" s="1" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -20339,7 +20341,7 @@
       <c r="K113" t="n">
         <v>294498.79</v>
       </c>
-      <c r="L113" t="n">
+      <c r="L113" s="2" t="n">
         <v>11.82</v>
       </c>
       <c r="M113" t="inlineStr">
@@ -20347,7 +20349,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
+      <c r="N113" s="1" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -20395,7 +20397,7 @@
       <c r="K114" t="n">
         <v>339339.04</v>
       </c>
-      <c r="L114" t="n">
+      <c r="L114" s="2" t="n">
         <v>0.72</v>
       </c>
       <c r="M114" t="inlineStr">
@@ -20403,7 +20405,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" s="1" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -20451,7 +20453,7 @@
       <c r="K115" t="n">
         <v>367583.44</v>
       </c>
-      <c r="L115" t="n">
+      <c r="L115" s="2" t="n">
         <v>2.03</v>
       </c>
       <c r="M115" t="inlineStr">
@@ -20459,7 +20461,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
+      <c r="N115" s="1" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -20507,7 +20509,7 @@
       <c r="K116" t="n">
         <v>294962.04</v>
       </c>
-      <c r="L116" t="n">
+      <c r="L116" s="2" t="n">
         <v>5.68</v>
       </c>
       <c r="M116" t="inlineStr">
@@ -20515,7 +20517,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" s="1" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -20563,7 +20565,7 @@
       <c r="K117" t="n">
         <v>322877.83</v>
       </c>
-      <c r="L117" t="n">
+      <c r="L117" s="2" t="n">
         <v>3.69</v>
       </c>
       <c r="M117" t="inlineStr">
@@ -20571,7 +20573,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" s="1" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -20619,7 +20621,7 @@
       <c r="K118" t="n">
         <v>281666.32</v>
       </c>
-      <c r="L118" t="n">
+      <c r="L118" s="2" t="n">
         <v>5.41</v>
       </c>
       <c r="M118" t="inlineStr">
@@ -20627,7 +20629,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" s="1" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -20675,7 +20677,7 @@
       <c r="K119" t="n">
         <v>295161.31</v>
       </c>
-      <c r="L119" t="n">
+      <c r="L119" s="2" t="n">
         <v>3.55</v>
       </c>
       <c r="M119" t="inlineStr">
@@ -20683,7 +20685,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" s="1" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -20727,7 +20729,7 @@
       <c r="K120" t="n">
         <v>310686.5</v>
       </c>
-      <c r="L120" t="n">
+      <c r="L120" s="2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M120" t="inlineStr">
@@ -20735,7 +20737,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" s="1" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -20783,7 +20785,7 @@
       <c r="K121" t="n">
         <v>287939.17</v>
       </c>
-      <c r="L121" t="n">
+      <c r="L121" s="2" t="n">
         <v>2.38</v>
       </c>
       <c r="M121" t="inlineStr">
@@ -20791,7 +20793,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" s="1" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -20835,7 +20837,7 @@
       <c r="K122" t="n">
         <v>292279.27</v>
       </c>
-      <c r="L122" t="n">
+      <c r="L122" s="2" t="n">
         <v>6.55</v>
       </c>
       <c r="M122" t="inlineStr">
@@ -20843,7 +20845,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" s="1" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -20891,7 +20893,7 @@
       <c r="K123" t="n">
         <v>324886.33</v>
       </c>
-      <c r="L123" t="n">
+      <c r="L123" s="2" t="n">
         <v>5.46</v>
       </c>
       <c r="M123" t="inlineStr">
@@ -20899,7 +20901,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" s="1" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -20947,7 +20949,7 @@
       <c r="K124" t="n">
         <v>323396.45</v>
       </c>
-      <c r="L124" t="n">
+      <c r="L124" s="2" t="n">
         <v>2.32</v>
       </c>
       <c r="M124" t="inlineStr">
@@ -20955,7 +20957,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" s="1" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -21003,7 +21005,7 @@
       <c r="K125" t="n">
         <v>33731.35</v>
       </c>
-      <c r="L125" t="n">
+      <c r="L125" s="2" t="n">
         <v>3.12</v>
       </c>
       <c r="M125" t="inlineStr">
@@ -21011,7 +21013,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" s="1" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -21059,7 +21061,7 @@
       <c r="K126" t="n">
         <v>307427.12</v>
       </c>
-      <c r="L126" t="n">
+      <c r="L126" s="2" t="n">
         <v>0.91</v>
       </c>
       <c r="M126" t="inlineStr">
@@ -21067,7 +21069,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" s="1" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -21115,7 +21117,7 @@
       <c r="K127" t="n">
         <v>356236.69</v>
       </c>
-      <c r="L127" t="n">
+      <c r="L127" s="2" t="n">
         <v>2.26</v>
       </c>
       <c r="M127" t="inlineStr">
@@ -21123,7 +21125,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" s="1" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -21171,7 +21173,7 @@
       <c r="K128" t="n">
         <v>337406.62</v>
       </c>
-      <c r="L128" t="n">
+      <c r="L128" s="2" t="n">
         <v>1.77</v>
       </c>
       <c r="M128" t="inlineStr">
@@ -21179,7 +21181,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" s="1" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -21227,7 +21229,7 @@
       <c r="K129" t="n">
         <v>400887.57</v>
       </c>
-      <c r="L129" t="n">
+      <c r="L129" s="2" t="n">
         <v>1.46</v>
       </c>
       <c r="M129" t="inlineStr">
@@ -21235,7 +21237,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" s="1" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -21283,7 +21285,7 @@
       <c r="K130" t="n">
         <v>350439.84</v>
       </c>
-      <c r="L130" t="n">
+      <c r="L130" s="2" t="n">
         <v>2.52</v>
       </c>
       <c r="M130" t="inlineStr">
@@ -21291,7 +21293,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" s="1" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -21339,7 +21341,7 @@
       <c r="K131" t="n">
         <v>301101.64</v>
       </c>
-      <c r="L131" t="n">
+      <c r="L131" s="2" t="n">
         <v>2.58</v>
       </c>
       <c r="M131" t="inlineStr">
@@ -21347,7 +21349,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" s="1" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -21395,7 +21397,7 @@
       <c r="K132" t="n">
         <v>330710.43</v>
       </c>
-      <c r="L132" t="n">
+      <c r="L132" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="M132" t="inlineStr">
@@ -21403,7 +21405,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" s="1" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -21451,7 +21453,7 @@
       <c r="K133" t="n">
         <v>337435.39</v>
       </c>
-      <c r="L133" t="n">
+      <c r="L133" s="2" t="n">
         <v>0.72</v>
       </c>
       <c r="M133" t="inlineStr">
@@ -21459,7 +21461,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" s="1" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -21507,7 +21509,7 @@
       <c r="K134" t="n">
         <v>281927.8</v>
       </c>
-      <c r="L134" t="n">
+      <c r="L134" s="2" t="n">
         <v>10.97</v>
       </c>
       <c r="M134" t="inlineStr">
@@ -21515,7 +21517,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
+      <c r="N134" s="1" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -21559,7 +21561,7 @@
       <c r="K135" t="n">
         <v>305101.84</v>
       </c>
-      <c r="L135" t="n">
+      <c r="L135" s="2" t="n">
         <v>3.98</v>
       </c>
       <c r="M135" t="inlineStr">
@@ -21567,7 +21569,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
+      <c r="N135" s="1" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -21615,7 +21617,7 @@
       <c r="K136" t="n">
         <v>406546.41</v>
       </c>
-      <c r="L136" t="n">
+      <c r="L136" s="2" t="n">
         <v>2.87</v>
       </c>
       <c r="M136" t="inlineStr">
@@ -21623,7 +21625,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
+      <c r="N136" s="1" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -21671,7 +21673,7 @@
       <c r="K137" t="n">
         <v>304592.09</v>
       </c>
-      <c r="L137" t="n">
+      <c r="L137" s="2" t="n">
         <v>2.06</v>
       </c>
       <c r="M137" t="inlineStr">
@@ -21679,7 +21681,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
+      <c r="N137" s="1" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -21727,7 +21729,7 @@
       <c r="K138" t="n">
         <v>284127.73</v>
       </c>
-      <c r="L138" t="n">
+      <c r="L138" s="2" t="n">
         <v>5.44</v>
       </c>
       <c r="M138" t="inlineStr">
@@ -21735,7 +21737,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" s="1" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -21783,7 +21785,7 @@
       <c r="K139" t="n">
         <v>317706.34</v>
       </c>
-      <c r="L139" t="n">
+      <c r="L139" s="2" t="n">
         <v>1.59</v>
       </c>
       <c r="M139" t="inlineStr">
@@ -21791,7 +21793,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" s="1" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -21839,7 +21841,7 @@
       <c r="K140" t="n">
         <v>319606.81</v>
       </c>
-      <c r="L140" t="n">
+      <c r="L140" s="2" t="n">
         <v>1.71</v>
       </c>
       <c r="M140" t="inlineStr">
@@ -21847,7 +21849,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" s="1" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -21895,7 +21897,7 @@
       <c r="K141" t="n">
         <v>356171.9</v>
       </c>
-      <c r="L141" t="n">
+      <c r="L141" s="2" t="n">
         <v>2.24</v>
       </c>
       <c r="M141" t="inlineStr">
@@ -21903,7 +21905,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" s="1" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -21951,7 +21953,7 @@
       <c r="K142" t="n">
         <v>373127.45</v>
       </c>
-      <c r="L142" t="n">
+      <c r="L142" s="2" t="n">
         <v>2.79</v>
       </c>
       <c r="M142" t="inlineStr">
@@ -21959,7 +21961,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" s="1" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -22007,7 +22009,7 @@
       <c r="K143" t="n">
         <v>319243.42</v>
       </c>
-      <c r="L143" t="n">
+      <c r="L143" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="M143" t="inlineStr">
@@ -22015,7 +22017,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
+      <c r="N143" s="1" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -22059,7 +22061,7 @@
       <c r="K144" t="n">
         <v>309922.15</v>
       </c>
-      <c r="L144" t="n">
+      <c r="L144" s="2" t="n">
         <v>2.51</v>
       </c>
       <c r="M144" t="inlineStr">
@@ -22067,7 +22069,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
+      <c r="N144" s="1" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -22115,7 +22117,7 @@
       <c r="K145" t="n">
         <v>369888.9</v>
       </c>
-      <c r="L145" t="n">
+      <c r="L145" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M145" t="inlineStr">
@@ -22123,7 +22125,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" s="1" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -22171,7 +22173,7 @@
       <c r="K146" t="n">
         <v>305339.58</v>
       </c>
-      <c r="L146" t="n">
+      <c r="L146" s="2" t="n">
         <v>6.06</v>
       </c>
       <c r="M146" t="inlineStr">
@@ -22179,7 +22181,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" s="1" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -22227,7 +22229,7 @@
       <c r="K147" t="n">
         <v>302105.42</v>
       </c>
-      <c r="L147" t="n">
+      <c r="L147" s="2" t="n">
         <v>2.23</v>
       </c>
       <c r="M147" t="inlineStr">
@@ -22235,7 +22237,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" s="1" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -22283,7 +22285,7 @@
       <c r="K148" t="n">
         <v>317440.92</v>
       </c>
-      <c r="L148" t="n">
+      <c r="L148" s="2" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="M148" t="inlineStr">
@@ -22341,7 +22343,7 @@
       <c r="K149" t="n">
         <v>3218395.2</v>
       </c>
-      <c r="L149" t="n">
+      <c r="L149" s="2" t="n">
         <v>1.67</v>
       </c>
       <c r="M149" t="inlineStr">
@@ -22349,7 +22351,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" s="1" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -22393,7 +22395,7 @@
       <c r="K150" t="n">
         <v>283854.3</v>
       </c>
-      <c r="L150" t="n">
+      <c r="L150" s="2" t="n">
         <v>5.12</v>
       </c>
       <c r="M150" t="inlineStr">
@@ -22401,7 +22403,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" s="1" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -22449,7 +22451,7 @@
       <c r="K151" t="n">
         <v>332339.55</v>
       </c>
-      <c r="L151" t="n">
+      <c r="L151" s="2" t="n">
         <v>1.96</v>
       </c>
       <c r="M151" t="inlineStr">
@@ -22457,7 +22459,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" s="1" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -22505,7 +22507,7 @@
       <c r="K152" t="n">
         <v>305983.2</v>
       </c>
-      <c r="L152" t="n">
+      <c r="L152" s="2" t="n">
         <v>2.21</v>
       </c>
       <c r="M152" t="inlineStr">
@@ -22513,7 +22515,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" s="1" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -22561,7 +22563,7 @@
       <c r="K153" t="n">
         <v>330279.79</v>
       </c>
-      <c r="L153" t="n">
+      <c r="L153" s="2" t="n">
         <v>0.67</v>
       </c>
       <c r="M153" t="inlineStr">
@@ -22569,7 +22571,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" s="1" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -22617,7 +22619,7 @@
       <c r="K154" t="n">
         <v>314797.74</v>
       </c>
-      <c r="L154" t="n">
+      <c r="L154" s="2" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="M154" t="inlineStr">
@@ -22625,7 +22627,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" s="1" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -22673,7 +22675,7 @@
       <c r="K155" t="n">
         <v>347246.31</v>
       </c>
-      <c r="L155" t="n">
+      <c r="L155" s="2" t="n">
         <v>0.31</v>
       </c>
       <c r="M155" t="inlineStr">
@@ -22681,7 +22683,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" s="1" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -22729,7 +22731,7 @@
       <c r="K156" t="n">
         <v>390534.58</v>
       </c>
-      <c r="L156" t="n">
+      <c r="L156" s="2" t="n">
         <v>0.74</v>
       </c>
       <c r="M156" t="inlineStr">
@@ -22737,7 +22739,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" s="1" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -22785,7 +22787,7 @@
       <c r="K157" t="n">
         <v>295533.99</v>
       </c>
-      <c r="L157" t="n">
+      <c r="L157" s="2" t="n">
         <v>2.99</v>
       </c>
       <c r="M157" t="inlineStr">
@@ -22793,7 +22795,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" s="1" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -22841,7 +22843,7 @@
       <c r="K158" t="n">
         <v>332303.37</v>
       </c>
-      <c r="L158" t="n">
+      <c r="L158" s="2" t="n">
         <v>5.14</v>
       </c>
       <c r="M158" t="inlineStr">
@@ -22899,7 +22901,7 @@
       <c r="K159" t="n">
         <v>317142.33</v>
       </c>
-      <c r="L159" t="n">
+      <c r="L159" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="M159" t="inlineStr">
@@ -22907,7 +22909,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
+      <c r="N159" s="1" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -22955,7 +22957,7 @@
       <c r="K160" t="n">
         <v>319006.51</v>
       </c>
-      <c r="L160" t="n">
+      <c r="L160" s="2" t="n">
         <v>0.37</v>
       </c>
       <c r="M160" t="inlineStr">
@@ -22963,7 +22965,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" s="1" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -23011,7 +23013,7 @@
       <c r="K161" t="n">
         <v>356768.84</v>
       </c>
-      <c r="L161" t="n">
+      <c r="L161" s="2" t="n">
         <v>2.16</v>
       </c>
       <c r="M161" t="inlineStr">
@@ -23019,7 +23021,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" s="1" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -23067,7 +23069,7 @@
       <c r="K162" t="n">
         <v>345818.87</v>
       </c>
-      <c r="L162" t="n">
+      <c r="L162" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="M162" t="inlineStr">
@@ -23075,7 +23077,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" s="1" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -23123,7 +23125,7 @@
       <c r="K163" t="n">
         <v>340278.77</v>
       </c>
-      <c r="L163" t="n">
+      <c r="L163" s="2" t="n">
         <v>2.81</v>
       </c>
       <c r="M163" t="inlineStr">
@@ -23131,7 +23133,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" s="1" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -23179,7 +23181,7 @@
       <c r="K164" t="n">
         <v>322790.56</v>
       </c>
-      <c r="L164" t="n">
+      <c r="L164" s="2" t="n">
         <v>0.45</v>
       </c>
       <c r="M164" t="inlineStr">
@@ -23187,7 +23189,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" s="1" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -23235,7 +23237,7 @@
       <c r="K165" t="n">
         <v>321196.77</v>
       </c>
-      <c r="L165" t="n">
+      <c r="L165" s="2" t="n">
         <v>2.31</v>
       </c>
       <c r="M165" t="inlineStr">
@@ -23243,7 +23245,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" s="1" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -23291,7 +23293,7 @@
       <c r="K166" t="n">
         <v>349245.06</v>
       </c>
-      <c r="L166" t="n">
+      <c r="L166" s="2" t="n">
         <v>0.61</v>
       </c>
       <c r="M166" t="inlineStr">
@@ -23299,7 +23301,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
+      <c r="N166" s="1" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -23347,7 +23349,7 @@
       <c r="K167" t="n">
         <v>392178.62</v>
       </c>
-      <c r="L167" t="n">
+      <c r="L167" s="2" t="n">
         <v>2.03</v>
       </c>
       <c r="M167" t="inlineStr">
@@ -23355,7 +23357,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" s="1" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -23403,7 +23405,7 @@
       <c r="K168" t="n">
         <v>353087.63</v>
       </c>
-      <c r="L168" t="n">
+      <c r="L168" s="2" t="n">
         <v>3.2</v>
       </c>
       <c r="M168" t="inlineStr">
@@ -23411,7 +23413,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" s="1" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -23459,7 +23461,7 @@
       <c r="K169" t="n">
         <v>339877.58</v>
       </c>
-      <c r="L169" t="n">
+      <c r="L169" s="2" t="n">
         <v>6.16</v>
       </c>
       <c r="M169" t="inlineStr">
@@ -23467,7 +23469,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" s="1" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -23515,7 +23517,7 @@
       <c r="K170" t="n">
         <v>392360.81</v>
       </c>
-      <c r="L170" t="n">
+      <c r="L170" s="2" t="n">
         <v>1.63</v>
       </c>
       <c r="M170" t="inlineStr">
@@ -23523,7 +23525,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" s="1" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -23571,7 +23573,7 @@
       <c r="K171" t="n">
         <v>373356.34</v>
       </c>
-      <c r="L171" t="n">
+      <c r="L171" s="2" t="n">
         <v>2.12</v>
       </c>
       <c r="M171" t="inlineStr">
@@ -23579,7 +23581,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" s="1" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -23627,7 +23629,7 @@
       <c r="K172" t="n">
         <v>363226.13</v>
       </c>
-      <c r="L172" t="n">
+      <c r="L172" s="2" t="n">
         <v>1.22</v>
       </c>
       <c r="M172" t="inlineStr">
@@ -23635,7 +23637,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" s="1" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -23683,7 +23685,7 @@
       <c r="K173" t="n">
         <v>321029.21</v>
       </c>
-      <c r="L173" t="n">
+      <c r="L173" s="2" t="n">
         <v>2.91</v>
       </c>
       <c r="M173" t="inlineStr">
@@ -23691,7 +23693,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
+      <c r="N173" s="1" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -23739,7 +23741,7 @@
       <c r="K174" t="n">
         <v>347977.38</v>
       </c>
-      <c r="L174" t="n">
+      <c r="L174" s="2" t="n">
         <v>0.83</v>
       </c>
       <c r="M174" t="inlineStr">
@@ -23747,7 +23749,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" s="1" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -23795,7 +23797,7 @@
       <c r="K175" t="n">
         <v>332382.59</v>
       </c>
-      <c r="L175" t="n">
+      <c r="L175" s="2" t="n">
         <v>1.33</v>
       </c>
       <c r="M175" t="inlineStr">
@@ -23803,7 +23805,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" s="1" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -23851,7 +23853,7 @@
       <c r="K176" t="n">
         <v>361470.36</v>
       </c>
-      <c r="L176" t="n">
+      <c r="L176" s="2" t="n">
         <v>1.77</v>
       </c>
       <c r="M176" t="inlineStr">
@@ -23859,7 +23861,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" s="1" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -23907,7 +23909,7 @@
       <c r="K177" t="n">
         <v>323939.2</v>
       </c>
-      <c r="L177" t="n">
+      <c r="L177" s="2" t="n">
         <v>3.86</v>
       </c>
       <c r="M177" t="inlineStr">
@@ -23915,7 +23917,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
+      <c r="N177" s="1" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -23963,7 +23965,7 @@
       <c r="K178" t="n">
         <v>365251.91</v>
       </c>
-      <c r="L178" t="n">
+      <c r="L178" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="M178" t="inlineStr">
@@ -23971,7 +23973,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
+      <c r="N178" s="1" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -24019,7 +24021,7 @@
       <c r="K179" t="n">
         <v>338567.6</v>
       </c>
-      <c r="L179" t="n">
+      <c r="L179" s="2" t="n">
         <v>2.27</v>
       </c>
       <c r="M179" t="inlineStr">
@@ -24027,7 +24029,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
+      <c r="N179" s="1" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -24075,7 +24077,7 @@
       <c r="K180" t="n">
         <v>312904.62</v>
       </c>
-      <c r="L180" t="n">
+      <c r="L180" s="2" t="n">
         <v>10.78</v>
       </c>
       <c r="M180" t="inlineStr">
@@ -24083,7 +24085,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
+      <c r="N180" s="1" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -24131,7 +24133,7 @@
       <c r="K181" t="n">
         <v>308480.65</v>
       </c>
-      <c r="L181" t="n">
+      <c r="L181" s="2" t="n">
         <v>1.19</v>
       </c>
       <c r="M181" t="inlineStr">
@@ -24139,7 +24141,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
+      <c r="N181" s="1" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -24187,7 +24189,7 @@
       <c r="K182" t="n">
         <v>342623.39</v>
       </c>
-      <c r="L182" t="n">
+      <c r="L182" s="2" t="n">
         <v>0.97</v>
       </c>
       <c r="M182" t="inlineStr">
@@ -24195,7 +24197,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" s="1" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -24243,7 +24245,7 @@
       <c r="K183" t="n">
         <v>452281.43</v>
       </c>
-      <c r="L183" t="n">
+      <c r="L183" s="2" t="n">
         <v>1.77</v>
       </c>
       <c r="M183" t="inlineStr">
@@ -24251,7 +24253,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" s="1" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -24295,7 +24297,7 @@
       <c r="K184" t="n">
         <v>325606.02</v>
       </c>
-      <c r="L184" t="n">
+      <c r="L184" s="2" t="n">
         <v>2.38</v>
       </c>
       <c r="M184" t="inlineStr">
@@ -24303,7 +24305,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" s="1" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -24351,7 +24353,7 @@
       <c r="K185" t="n">
         <v>398064.84</v>
       </c>
-      <c r="L185" t="n">
+      <c r="L185" s="2" t="n">
         <v>5.21</v>
       </c>
       <c r="M185" t="inlineStr">
@@ -24359,7 +24361,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" s="1" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -24403,7 +24405,7 @@
       <c r="K186" t="n">
         <v>341476.17</v>
       </c>
-      <c r="L186" t="n">
+      <c r="L186" s="2" t="n">
         <v>1.79</v>
       </c>
       <c r="M186" t="inlineStr">
@@ -24411,7 +24413,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" s="1" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -24459,7 +24461,7 @@
       <c r="K187" t="n">
         <v>384557.49</v>
       </c>
-      <c r="L187" t="n">
+      <c r="L187" s="2" t="n">
         <v>6.67</v>
       </c>
       <c r="M187" t="inlineStr">
@@ -24467,7 +24469,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" s="1" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -24515,7 +24517,7 @@
       <c r="K188" t="n">
         <v>372016.77</v>
       </c>
-      <c r="L188" t="n">
+      <c r="L188" s="2" t="n">
         <v>0.61</v>
       </c>
       <c r="M188" t="inlineStr">
@@ -24523,7 +24525,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" s="1" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -24571,7 +24573,7 @@
       <c r="K189" t="n">
         <v>399999.6</v>
       </c>
-      <c r="L189" t="n">
+      <c r="L189" s="2" t="n">
         <v>3.8</v>
       </c>
       <c r="M189" t="inlineStr">
@@ -24579,7 +24581,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" s="1" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -24627,7 +24629,7 @@
       <c r="K190" t="n">
         <v>347811.75</v>
       </c>
-      <c r="L190" t="n">
+      <c r="L190" s="2" t="n">
         <v>2.71</v>
       </c>
       <c r="M190" t="inlineStr">
@@ -24635,7 +24637,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
+      <c r="N190" s="1" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -24683,7 +24685,7 @@
       <c r="K191" t="n">
         <v>310195.41</v>
       </c>
-      <c r="L191" t="n">
+      <c r="L191" s="2" t="n">
         <v>1.93</v>
       </c>
       <c r="M191" t="inlineStr">
@@ -24691,7 +24693,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" s="1" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -24739,7 +24741,7 @@
       <c r="K192" t="n">
         <v>414945.39</v>
       </c>
-      <c r="L192" t="n">
+      <c r="L192" s="2" t="n">
         <v>1.14</v>
       </c>
       <c r="M192" t="inlineStr">
@@ -24747,7 +24749,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" s="1" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -24795,7 +24797,7 @@
       <c r="K193" t="n">
         <v>404758.22</v>
       </c>
-      <c r="L193" t="n">
+      <c r="L193" s="2" t="n">
         <v>1.71</v>
       </c>
       <c r="M193" t="inlineStr">
@@ -24803,7 +24805,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
+      <c r="N193" s="1" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -24851,7 +24853,7 @@
       <c r="K194" t="n">
         <v>514030</v>
       </c>
-      <c r="L194" t="n">
+      <c r="L194" s="2" t="n">
         <v>6.54</v>
       </c>
       <c r="M194" t="inlineStr">
@@ -24859,7 +24861,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
+      <c r="N194" s="1" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -24907,7 +24909,7 @@
       <c r="K195" t="n">
         <v>312562</v>
       </c>
-      <c r="L195" t="n">
+      <c r="L195" s="2" t="n">
         <v>1.4</v>
       </c>
       <c r="M195" t="inlineStr">
@@ -24915,7 +24917,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr"/>
+      <c r="N195" s="1" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -24963,7 +24965,7 @@
       <c r="K196" t="n">
         <v>3262485.2</v>
       </c>
-      <c r="L196" t="n">
+      <c r="L196" s="2" t="n">
         <v>5.49</v>
       </c>
       <c r="M196" t="inlineStr">
@@ -24971,7 +24973,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
+      <c r="N196" s="1" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -25019,7 +25021,7 @@
       <c r="K197" t="n">
         <v>325854.52</v>
       </c>
-      <c r="L197" t="n">
+      <c r="L197" s="2" t="n">
         <v>6.18</v>
       </c>
       <c r="M197" t="inlineStr">
@@ -25027,7 +25029,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" s="1" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -25075,7 +25077,7 @@
       <c r="K198" t="n">
         <v>353234.47</v>
       </c>
-      <c r="L198" t="n">
+      <c r="L198" s="2" t="n">
         <v>2.72</v>
       </c>
       <c r="M198" t="inlineStr">
@@ -25083,7 +25085,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
+      <c r="N198" s="1" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -25131,7 +25133,7 @@
       <c r="K199" t="n">
         <v>321835.32</v>
       </c>
-      <c r="L199" t="n">
+      <c r="L199" s="2" t="n">
         <v>2.71</v>
       </c>
       <c r="M199" t="inlineStr">
@@ -25139,7 +25141,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
+      <c r="N199" s="1" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -25187,7 +25189,7 @@
       <c r="K200" t="n">
         <v>389366.25</v>
       </c>
-      <c r="L200" t="n">
+      <c r="L200" s="2" t="n">
         <v>4.45</v>
       </c>
       <c r="M200" t="inlineStr">
@@ -25195,7 +25197,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" s="1" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -25243,7 +25245,7 @@
       <c r="K201" t="n">
         <v>424455.38</v>
       </c>
-      <c r="L201" t="n">
+      <c r="L201" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="M201" t="inlineStr">
@@ -25251,7 +25253,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
+      <c r="N201" s="1" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -25299,7 +25301,7 @@
       <c r="K202" t="n">
         <v>316400.3</v>
       </c>
-      <c r="L202" t="n">
+      <c r="L202" s="2" t="n">
         <v>10.6</v>
       </c>
       <c r="M202" t="inlineStr">
@@ -25307,7 +25309,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" s="1" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -25355,7 +25357,7 @@
       <c r="K203" t="n">
         <v>338999.52</v>
       </c>
-      <c r="L203" t="n">
+      <c r="L203" s="2" t="n">
         <v>4.85</v>
       </c>
       <c r="M203" t="inlineStr">
@@ -25363,7 +25365,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" s="1" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -25411,7 +25413,7 @@
       <c r="K204" t="n">
         <v>276190.3</v>
       </c>
-      <c r="L204" t="n">
+      <c r="L204" s="2" t="n">
         <v>4.14</v>
       </c>
       <c r="M204" t="inlineStr">
@@ -25419,7 +25421,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" s="1" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -25467,7 +25469,7 @@
       <c r="K205" t="n">
         <v>379766.12</v>
       </c>
-      <c r="L205" t="n">
+      <c r="L205" s="2" t="n">
         <v>1.41</v>
       </c>
       <c r="M205" t="inlineStr">
@@ -25475,7 +25477,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" s="1" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -25523,7 +25525,7 @@
       <c r="K206" t="n">
         <v>547114.45</v>
       </c>
-      <c r="L206" t="n">
+      <c r="L206" s="2" t="n">
         <v>0.43</v>
       </c>
       <c r="M206" t="inlineStr">
@@ -25531,7 +25533,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" s="1" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -25579,7 +25581,7 @@
       <c r="K207" t="n">
         <v>350561.34</v>
       </c>
-      <c r="L207" t="n">
+      <c r="L207" s="2" t="n">
         <v>2.06</v>
       </c>
       <c r="M207" t="inlineStr">
@@ -25587,7 +25589,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
+      <c r="N207" s="1" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -25635,7 +25637,7 @@
       <c r="K208" t="n">
         <v>276678.47</v>
       </c>
-      <c r="L208" t="n">
+      <c r="L208" s="2" t="n">
         <v>8.779999999999999</v>
       </c>
       <c r="M208" t="inlineStr">
@@ -25643,7 +25645,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" s="1" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -25687,7 +25689,7 @@
       <c r="K209" t="n">
         <v>290587.85</v>
       </c>
-      <c r="L209" t="n">
+      <c r="L209" s="2" t="n">
         <v>1.28</v>
       </c>
       <c r="M209" t="inlineStr">
@@ -25695,7 +25697,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
+      <c r="N209" s="1" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25743,7 +25745,7 @@
       <c r="K210" t="n">
         <v>386030.93</v>
       </c>
-      <c r="L210" t="n">
+      <c r="L210" s="2" t="n">
         <v>1.96</v>
       </c>
       <c r="M210" t="inlineStr">
@@ -25751,7 +25753,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
+      <c r="N210" s="1" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25799,7 +25801,7 @@
       <c r="K211" t="n">
         <v>408288.77</v>
       </c>
-      <c r="L211" t="n">
+      <c r="L211" s="2" t="n">
         <v>0.54</v>
       </c>
       <c r="M211" t="inlineStr">
@@ -25807,7 +25809,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
+      <c r="N211" s="1" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25855,7 +25857,7 @@
       <c r="K212" t="n">
         <v>3942527.5</v>
       </c>
-      <c r="L212" t="n">
+      <c r="L212" s="2" t="n">
         <v>1.06</v>
       </c>
       <c r="M212" t="inlineStr">
@@ -25863,7 +25865,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
+      <c r="N212" s="1" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25911,7 +25913,7 @@
       <c r="K213" t="n">
         <v>324876.75</v>
       </c>
-      <c r="L213" t="n">
+      <c r="L213" s="2" t="n">
         <v>2.16</v>
       </c>
       <c r="M213" t="inlineStr">
@@ -25919,7 +25921,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" s="1" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25967,7 +25969,7 @@
       <c r="K214" t="n">
         <v>299925.65</v>
       </c>
-      <c r="L214" t="n">
+      <c r="L214" s="2" t="n">
         <v>1.64</v>
       </c>
       <c r="M214" t="inlineStr">
@@ -25975,7 +25977,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
+      <c r="N214" s="1" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -26023,7 +26025,7 @@
       <c r="K215" t="n">
         <v>320048.65</v>
       </c>
-      <c r="L215" t="n">
+      <c r="L215" s="2" t="n">
         <v>0.74</v>
       </c>
       <c r="M215" t="inlineStr">
@@ -26031,7 +26033,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" s="1" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -26075,7 +26077,7 @@
       <c r="K216" t="n">
         <v>314012.72</v>
       </c>
-      <c r="L216" t="n">
+      <c r="L216" s="2" t="n">
         <v>3.73</v>
       </c>
       <c r="M216" t="inlineStr">
@@ -26083,7 +26085,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
+      <c r="N216" s="1" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -26131,7 +26133,7 @@
       <c r="K217" t="n">
         <v>370486.89</v>
       </c>
-      <c r="L217" t="n">
+      <c r="L217" s="2" t="n">
         <v>6.85</v>
       </c>
       <c r="M217" t="inlineStr">
@@ -26139,7 +26141,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
+      <c r="N217" s="1" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -26187,7 +26189,7 @@
       <c r="K218" t="n">
         <v>301964.46</v>
       </c>
-      <c r="L218" t="n">
+      <c r="L218" s="2" t="n">
         <v>4.49</v>
       </c>
       <c r="M218" t="inlineStr">
@@ -26195,7 +26197,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
+      <c r="N218" s="1" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26243,7 +26245,7 @@
       <c r="K219" t="n">
         <v>318586.76</v>
       </c>
-      <c r="L219" t="n">
+      <c r="L219" s="2" t="n">
         <v>2.69</v>
       </c>
       <c r="M219" t="inlineStr">
@@ -26251,7 +26253,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
+      <c r="N219" s="1" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26299,7 +26301,7 @@
       <c r="K220" t="n">
         <v>551965.24</v>
       </c>
-      <c r="L220" t="n">
+      <c r="L220" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="M220" t="inlineStr">
@@ -26307,7 +26309,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
+      <c r="N220" s="1" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26355,7 +26357,7 @@
       <c r="K221" t="n">
         <v>537522.29</v>
       </c>
-      <c r="L221" t="n">
+      <c r="L221" s="2" t="n">
         <v>1.77</v>
       </c>
       <c r="M221" t="inlineStr">
@@ -26363,7 +26365,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
+      <c r="N221" s="1" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26411,7 +26413,7 @@
       <c r="K222" t="n">
         <v>383521.57</v>
       </c>
-      <c r="L222" t="n">
+      <c r="L222" s="2" t="n">
         <v>1.3</v>
       </c>
       <c r="M222" t="inlineStr">
@@ -26419,7 +26421,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
+      <c r="N222" s="1" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -26467,7 +26469,7 @@
       <c r="K223" t="n">
         <v>353854.91</v>
       </c>
-      <c r="L223" t="n">
+      <c r="L223" s="2" t="n">
         <v>1.54</v>
       </c>
       <c r="M223" t="inlineStr">
@@ -26475,7 +26477,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" s="1" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26523,7 +26525,7 @@
       <c r="K224" t="n">
         <v>364941.7</v>
       </c>
-      <c r="L224" t="n">
+      <c r="L224" s="2" t="n">
         <v>8.5</v>
       </c>
       <c r="M224" t="inlineStr">
@@ -26531,7 +26533,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
+      <c r="N224" s="1" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26579,7 +26581,7 @@
       <c r="K225" t="n">
         <v>314917.8</v>
       </c>
-      <c r="L225" t="n">
+      <c r="L225" s="2" t="n">
         <v>11.58</v>
       </c>
       <c r="M225" t="inlineStr">
@@ -26587,7 +26589,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
+      <c r="N225" s="1" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26631,7 +26633,7 @@
       <c r="K226" t="n">
         <v>344492.48</v>
       </c>
-      <c r="L226" t="n">
+      <c r="L226" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M226" t="inlineStr">
@@ -26639,7 +26641,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
+      <c r="N226" s="1" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26687,7 +26689,7 @@
       <c r="K227" t="n">
         <v>367694.81</v>
       </c>
-      <c r="L227" t="n">
+      <c r="L227" s="2" t="n">
         <v>1.78</v>
       </c>
       <c r="M227" t="inlineStr">
@@ -26695,7 +26697,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
+      <c r="N227" s="1" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26743,7 +26745,7 @@
       <c r="K228" t="n">
         <v>352035.66</v>
       </c>
-      <c r="L228" t="n">
+      <c r="L228" s="2" t="n">
         <v>1.78</v>
       </c>
       <c r="M228" t="inlineStr">
@@ -26751,7 +26753,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
+      <c r="N228" s="1" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26799,7 +26801,7 @@
       <c r="K229" t="n">
         <v>736539.92</v>
       </c>
-      <c r="L229" t="n">
+      <c r="L229" s="2" t="n">
         <v>6.54</v>
       </c>
       <c r="M229" t="inlineStr">
@@ -26807,7 +26809,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
+      <c r="N229" s="1" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26855,7 +26857,7 @@
       <c r="K230" t="n">
         <v>372411.6</v>
       </c>
-      <c r="L230" t="n">
+      <c r="L230" s="2" t="n">
         <v>6.6</v>
       </c>
       <c r="M230" t="inlineStr">
@@ -26863,7 +26865,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
+      <c r="N230" s="1" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26911,7 +26913,7 @@
       <c r="K231" t="n">
         <v>352399.66</v>
       </c>
-      <c r="L231" t="n">
+      <c r="L231" s="2" t="n">
         <v>5.36</v>
       </c>
       <c r="M231" t="inlineStr">
@@ -26919,7 +26921,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
+      <c r="N231" s="1" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26967,7 +26969,7 @@
       <c r="K232" t="n">
         <v>302109.97</v>
       </c>
-      <c r="L232" t="n">
+      <c r="L232" s="2" t="n">
         <v>6.87</v>
       </c>
       <c r="M232" t="inlineStr">
@@ -26975,7 +26977,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
+      <c r="N232" s="1" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -27023,7 +27025,7 @@
       <c r="K233" t="n">
         <v>269911.07</v>
       </c>
-      <c r="L233" t="n">
+      <c r="L233" s="2" t="n">
         <v>11.06</v>
       </c>
       <c r="M233" t="inlineStr">
@@ -27081,7 +27083,7 @@
       <c r="K234" t="n">
         <v>383782.7</v>
       </c>
-      <c r="L234" t="n">
+      <c r="L234" s="2" t="n">
         <v>5.99</v>
       </c>
       <c r="M234" t="inlineStr">
@@ -27139,7 +27141,7 @@
       <c r="K235" t="n">
         <v>362151.31</v>
       </c>
-      <c r="L235" t="n">
+      <c r="L235" s="2" t="n">
         <v>0.28</v>
       </c>
       <c r="M235" t="inlineStr">
@@ -27147,7 +27149,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
+      <c r="N235" s="1" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27195,7 +27197,7 @@
       <c r="K236" t="n">
         <v>408873.63</v>
       </c>
-      <c r="L236" t="n">
+      <c r="L236" s="2" t="n">
         <v>1.15</v>
       </c>
       <c r="M236" t="inlineStr">
@@ -27203,7 +27205,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
+      <c r="N236" s="1" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27251,7 +27253,7 @@
       <c r="K237" t="n">
         <v>325748.24</v>
       </c>
-      <c r="L237" t="n">
+      <c r="L237" s="2" t="n">
         <v>1.23</v>
       </c>
       <c r="M237" t="inlineStr">
@@ -27259,7 +27261,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
+      <c r="N237" s="1" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27307,7 +27309,7 @@
       <c r="K238" t="n">
         <v>321141.55</v>
       </c>
-      <c r="L238" t="n">
+      <c r="L238" s="2" t="n">
         <v>2.23</v>
       </c>
       <c r="M238" t="inlineStr">
@@ -27315,7 +27317,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
+      <c r="N238" s="1" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27363,7 +27365,7 @@
       <c r="K239" t="n">
         <v>383173.5</v>
       </c>
-      <c r="L239" t="n">
+      <c r="L239" s="2" t="n">
         <v>1.88</v>
       </c>
       <c r="M239" t="inlineStr">
@@ -27371,7 +27373,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
+      <c r="N239" s="1" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27419,7 +27421,7 @@
       <c r="K240" t="n">
         <v>379848.98</v>
       </c>
-      <c r="L240" t="n">
+      <c r="L240" s="2" t="n">
         <v>1.01</v>
       </c>
       <c r="M240" t="inlineStr">
@@ -27427,7 +27429,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
+      <c r="N240" s="1" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27475,7 +27477,7 @@
       <c r="K241" t="n">
         <v>428646.59</v>
       </c>
-      <c r="L241" t="n">
+      <c r="L241" s="2" t="n">
         <v>1.09</v>
       </c>
       <c r="M241" t="inlineStr">
@@ -27483,7 +27485,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
+      <c r="N241" s="1" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27531,7 +27533,7 @@
       <c r="K242" t="n">
         <v>607402.13</v>
       </c>
-      <c r="L242" t="n">
+      <c r="L242" s="2" t="n">
         <v>3.09</v>
       </c>
       <c r="M242" t="inlineStr">
@@ -27539,7 +27541,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr"/>
+      <c r="N242" s="1" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27587,7 +27589,7 @@
       <c r="K243" t="n">
         <v>377758.72</v>
       </c>
-      <c r="L243" t="n">
+      <c r="L243" s="2" t="n">
         <v>3.22</v>
       </c>
       <c r="M243" t="inlineStr">
@@ -27595,7 +27597,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr"/>
+      <c r="N243" s="1" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27643,7 +27645,7 @@
       <c r="K244" t="n">
         <v>376213.02</v>
       </c>
-      <c r="L244" t="n">
+      <c r="L244" s="2" t="n">
         <v>0.41</v>
       </c>
       <c r="M244" t="inlineStr">
@@ -27701,7 +27703,7 @@
       <c r="K245" t="n">
         <v>299866.8</v>
       </c>
-      <c r="L245" t="n">
+      <c r="L245" s="2" t="n">
         <v>3.28</v>
       </c>
       <c r="M245" t="inlineStr">
@@ -27709,7 +27711,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
+      <c r="N245" s="1" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27757,7 +27759,7 @@
       <c r="K246" t="n">
         <v>344775</v>
       </c>
-      <c r="L246" t="n">
+      <c r="L246" s="2" t="n">
         <v>1.29</v>
       </c>
       <c r="M246" t="inlineStr">
@@ -27765,7 +27767,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
+      <c r="N246" s="1" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27813,7 +27815,7 @@
       <c r="K247" t="n">
         <v>319087.58</v>
       </c>
-      <c r="L247" t="n">
+      <c r="L247" s="2" t="n">
         <v>9.44</v>
       </c>
       <c r="M247" t="inlineStr">
@@ -27821,7 +27823,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr"/>
+      <c r="N247" s="1" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27869,7 +27871,7 @@
       <c r="K248" t="n">
         <v>374297.92</v>
       </c>
-      <c r="L248" t="n">
+      <c r="L248" s="2" t="n">
         <v>1.37</v>
       </c>
       <c r="M248" t="inlineStr">
@@ -27877,7 +27879,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr"/>
+      <c r="N248" s="1" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27925,7 +27927,7 @@
       <c r="K249" t="n">
         <v>349484.11</v>
       </c>
-      <c r="L249" t="n">
+      <c r="L249" s="2" t="n">
         <v>4.99</v>
       </c>
       <c r="M249" t="inlineStr">
@@ -27933,7 +27935,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr"/>
+      <c r="N249" s="1" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27981,7 +27983,7 @@
       <c r="K250" t="n">
         <v>388374.51</v>
       </c>
-      <c r="L250" t="n">
+      <c r="L250" s="2" t="n">
         <v>2.68</v>
       </c>
       <c r="M250" t="inlineStr">
@@ -27989,7 +27991,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr"/>
+      <c r="N250" s="1" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28037,7 +28039,7 @@
       <c r="K251" t="n">
         <v>336946.2</v>
       </c>
-      <c r="L251" t="n">
+      <c r="L251" s="2" t="n">
         <v>1.63</v>
       </c>
       <c r="M251" t="inlineStr">
@@ -28045,7 +28047,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr"/>
+      <c r="N251" s="1" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28093,7 +28095,7 @@
       <c r="K252" t="n">
         <v>329672.68</v>
       </c>
-      <c r="L252" t="n">
+      <c r="L252" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="M252" t="inlineStr">
@@ -28101,7 +28103,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr"/>
+      <c r="N252" s="1" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28149,7 +28151,7 @@
       <c r="K253" t="n">
         <v>558631.23</v>
       </c>
-      <c r="L253" t="n">
+      <c r="L253" s="2" t="n">
         <v>1.04</v>
       </c>
       <c r="M253" t="inlineStr">
@@ -28157,7 +28159,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr"/>
+      <c r="N253" s="1" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28205,7 +28207,7 @@
       <c r="K254" t="n">
         <v>316589.3</v>
       </c>
-      <c r="L254" t="n">
+      <c r="L254" s="2" t="n">
         <v>1.76</v>
       </c>
       <c r="M254" t="inlineStr">
@@ -28213,7 +28215,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr"/>
+      <c r="N254" s="1" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28261,7 +28263,7 @@
       <c r="K255" t="n">
         <v>341133.83</v>
       </c>
-      <c r="L255" t="n">
+      <c r="L255" s="2" t="n">
         <v>1.08</v>
       </c>
       <c r="M255" t="inlineStr">
@@ -28269,7 +28271,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N255" t="inlineStr"/>
+      <c r="N255" s="1" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28313,7 +28315,7 @@
       <c r="K256" t="n">
         <v>367534.6</v>
       </c>
-      <c r="L256" t="n">
+      <c r="L256" s="2" t="n">
         <v>0.35</v>
       </c>
       <c r="M256" t="inlineStr">
@@ -28321,7 +28323,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N256" t="inlineStr"/>
+      <c r="N256" s="1" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28369,7 +28371,7 @@
       <c r="K257" t="n">
         <v>309161.87</v>
       </c>
-      <c r="L257" t="n">
+      <c r="L257" s="2" t="n">
         <v>4.44</v>
       </c>
       <c r="M257" t="inlineStr">
@@ -28377,7 +28379,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr"/>
+      <c r="N257" s="1" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28425,7 +28427,7 @@
       <c r="K258" t="n">
         <v>328209.31</v>
       </c>
-      <c r="L258" t="n">
+      <c r="L258" s="2" t="n">
         <v>9.77</v>
       </c>
       <c r="M258" t="inlineStr">
@@ -28483,7 +28485,7 @@
       <c r="K259" t="n">
         <v>333722.94</v>
       </c>
-      <c r="L259" t="n">
+      <c r="L259" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="M259" t="inlineStr">
@@ -28491,7 +28493,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N259" t="inlineStr"/>
+      <c r="N259" s="1" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28539,7 +28541,7 @@
       <c r="K260" t="n">
         <v>339798.38</v>
       </c>
-      <c r="L260" t="n">
+      <c r="L260" s="2" t="n">
         <v>0.95</v>
       </c>
       <c r="M260" t="inlineStr">
@@ -28547,7 +28549,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr"/>
+      <c r="N260" s="1" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28595,7 +28597,7 @@
       <c r="K261" t="n">
         <v>304900.65</v>
       </c>
-      <c r="L261" t="n">
+      <c r="L261" s="2" t="n">
         <v>2.4</v>
       </c>
       <c r="M261" t="inlineStr">
@@ -28603,7 +28605,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr"/>
+      <c r="N261" s="1" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28651,7 +28653,7 @@
       <c r="K262" t="n">
         <v>330039.2</v>
       </c>
-      <c r="L262" t="n">
+      <c r="L262" s="2" t="n">
         <v>0.77</v>
       </c>
       <c r="M262" t="inlineStr">
@@ -28659,7 +28661,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr"/>
+      <c r="N262" s="1" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28707,7 +28709,7 @@
       <c r="K263" t="n">
         <v>323505.41</v>
       </c>
-      <c r="L263" t="n">
+      <c r="L263" s="2" t="n">
         <v>6.22</v>
       </c>
       <c r="M263" t="inlineStr">
@@ -28715,7 +28717,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr"/>
+      <c r="N263" s="1" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28763,7 +28765,7 @@
       <c r="K264" t="n">
         <v>303121.34</v>
       </c>
-      <c r="L264" t="n">
+      <c r="L264" s="2" t="n">
         <v>11.46</v>
       </c>
       <c r="M264" t="inlineStr">
@@ -28771,7 +28773,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr"/>
+      <c r="N264" s="1" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28819,7 +28821,7 @@
       <c r="K265" t="n">
         <v>360645.27</v>
       </c>
-      <c r="L265" t="n">
+      <c r="L265" s="2" t="n">
         <v>0.35</v>
       </c>
       <c r="M265" t="inlineStr">
@@ -28827,7 +28829,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr"/>
+      <c r="N265" s="1" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28875,7 +28877,7 @@
       <c r="K266" t="n">
         <v>651331.6899999999</v>
       </c>
-      <c r="L266" t="n">
+      <c r="L266" s="2" t="n">
         <v>10.95</v>
       </c>
       <c r="M266" t="inlineStr">
@@ -28883,7 +28885,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr"/>
+      <c r="N266" s="1" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28931,7 +28933,7 @@
       <c r="K267" t="n">
         <v>286518.78</v>
       </c>
-      <c r="L267" t="n">
+      <c r="L267" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="M267" t="inlineStr">
@@ -28939,7 +28941,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr"/>
+      <c r="N267" s="1" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -28987,7 +28989,7 @@
       <c r="K268" t="n">
         <v>355527.4</v>
       </c>
-      <c r="L268" t="n">
+      <c r="L268" s="2" t="n">
         <v>3.83</v>
       </c>
       <c r="M268" t="inlineStr">
@@ -28995,7 +28997,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr"/>
+      <c r="N268" s="1" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29043,7 +29045,7 @@
       <c r="K269" t="n">
         <v>343003.46</v>
       </c>
-      <c r="L269" t="n">
+      <c r="L269" s="2" t="n">
         <v>2.02</v>
       </c>
       <c r="M269" t="inlineStr">
@@ -29051,7 +29053,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr"/>
+      <c r="N269" s="1" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29099,7 +29101,7 @@
       <c r="K270" t="n">
         <v>406831.63</v>
       </c>
-      <c r="L270" t="n">
+      <c r="L270" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="M270" t="inlineStr">
@@ -29107,7 +29109,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr"/>
+      <c r="N270" s="1" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29155,7 +29157,7 @@
       <c r="K271" t="n">
         <v>344756.38</v>
       </c>
-      <c r="L271" t="n">
+      <c r="L271" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="M271" t="inlineStr">
@@ -29163,7 +29165,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N271" t="inlineStr"/>
+      <c r="N271" s="1" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29211,7 +29213,7 @@
       <c r="K272" t="n">
         <v>326278.27</v>
       </c>
-      <c r="L272" t="n">
+      <c r="L272" s="2" t="n">
         <v>0.71</v>
       </c>
       <c r="M272" t="inlineStr">
@@ -29219,7 +29221,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr"/>
+      <c r="N272" s="1" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29267,7 +29269,7 @@
       <c r="K273" t="n">
         <v>329142</v>
       </c>
-      <c r="L273" t="n">
+      <c r="L273" s="2" t="n">
         <v>0.44</v>
       </c>
       <c r="M273" t="inlineStr">
@@ -29275,7 +29277,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr"/>
+      <c r="N273" s="1" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29323,7 +29325,7 @@
       <c r="K274" t="n">
         <v>324911.79</v>
       </c>
-      <c r="L274" t="n">
+      <c r="L274" s="2" t="n">
         <v>1.94</v>
       </c>
       <c r="M274" t="inlineStr">
@@ -29331,7 +29333,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr"/>
+      <c r="N274" s="1" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29379,7 +29381,7 @@
       <c r="K275" t="n">
         <v>369785</v>
       </c>
-      <c r="L275" t="n">
+      <c r="L275" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="M275" t="inlineStr">
@@ -29387,7 +29389,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N275" t="inlineStr"/>
+      <c r="N275" s="1" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -29435,7 +29437,7 @@
       <c r="K276" t="n">
         <v>369750.85</v>
       </c>
-      <c r="L276" t="n">
+      <c r="L276" s="2" t="n">
         <v>3.43</v>
       </c>
       <c r="M276" t="inlineStr">
@@ -29443,7 +29445,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr"/>
+      <c r="N276" s="1" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -29491,7 +29493,7 @@
       <c r="K277" t="n">
         <v>305837.45</v>
       </c>
-      <c r="L277" t="n">
+      <c r="L277" s="2" t="n">
         <v>10.26</v>
       </c>
       <c r="M277" t="inlineStr">
@@ -29499,7 +29501,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr"/>
+      <c r="N277" s="1" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -29547,7 +29549,7 @@
       <c r="K278" t="n">
         <v>404026.83</v>
       </c>
-      <c r="L278" t="n">
+      <c r="L278" s="2" t="n">
         <v>2.81</v>
       </c>
       <c r="M278" t="inlineStr">
@@ -29555,7 +29557,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr"/>
+      <c r="N278" s="1" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -29603,7 +29605,7 @@
       <c r="K279" t="n">
         <v>359475.28</v>
       </c>
-      <c r="L279" t="n">
+      <c r="L279" s="2" t="n">
         <v>5.3</v>
       </c>
       <c r="M279" t="inlineStr">
@@ -29611,7 +29613,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr"/>
+      <c r="N279" s="1" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -29659,7 +29661,7 @@
       <c r="K280" t="n">
         <v>375177.71</v>
       </c>
-      <c r="L280" t="n">
+      <c r="L280" s="2" t="n">
         <v>4.32</v>
       </c>
       <c r="M280" t="inlineStr">
@@ -29667,7 +29669,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N280" t="inlineStr"/>
+      <c r="N280" s="1" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -29715,7 +29717,7 @@
       <c r="K281" t="n">
         <v>289906.13</v>
       </c>
-      <c r="L281" t="n">
+      <c r="L281" s="2" t="n">
         <v>6.48</v>
       </c>
       <c r="M281" t="inlineStr">
@@ -29723,7 +29725,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N281" t="inlineStr"/>
+      <c r="N281" s="1" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -29771,7 +29773,7 @@
       <c r="K282" t="n">
         <v>447032.7</v>
       </c>
-      <c r="L282" t="n">
+      <c r="L282" s="2" t="n">
         <v>2.97</v>
       </c>
       <c r="M282" t="inlineStr">
@@ -29779,7 +29781,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr"/>
+      <c r="N282" s="1" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -29827,7 +29829,7 @@
       <c r="K283" t="n">
         <v>390671.35</v>
       </c>
-      <c r="L283" t="n">
+      <c r="L283" s="2" t="n">
         <v>0.93</v>
       </c>
       <c r="M283" t="inlineStr">
@@ -29835,7 +29837,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr"/>
+      <c r="N283" s="1" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -29883,7 +29885,7 @@
       <c r="K284" t="n">
         <v>332236.94</v>
       </c>
-      <c r="L284" t="n">
+      <c r="L284" s="2" t="n">
         <v>0.41</v>
       </c>
       <c r="M284" t="inlineStr">
@@ -29891,7 +29893,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr"/>
+      <c r="N284" s="1" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29939,7 +29941,7 @@
       <c r="K285" t="n">
         <v>423019.54</v>
       </c>
-      <c r="L285" t="n">
+      <c r="L285" s="2" t="n">
         <v>1.81</v>
       </c>
       <c r="M285" t="inlineStr">
@@ -29947,7 +29949,7 @@
           <t>Ativa</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr"/>
+      <c r="N285" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados/brutos/comercial_espelho.xlsx
+++ b/dados/brutos/comercial_espelho.xlsx
@@ -55,7 +55,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
